--- a/data/trans_camb/P19C04-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C04-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 14,06</t>
+          <t>3,8; 14,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 5,5</t>
+          <t>-5,28; 5,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 6,2</t>
+          <t>-4,81; 5,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 8,75</t>
+          <t>-0,25; 8,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,29</t>
+          <t>-2,89; 5,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 5,2</t>
+          <t>-1,82; 5,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 10,21</t>
+          <t>3,26; 10,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,39</t>
+          <t>-2,17; 4,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 4,6</t>
+          <t>-1,44; 4,78</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 75,05</t>
+          <t>15,72; 76,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 28,48</t>
+          <t>-21,98; 27,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 32,54</t>
+          <t>-19,61; 33,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 76,14</t>
+          <t>-2,41; 69,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 45,28</t>
+          <t>-18,92; 43,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 46,99</t>
+          <t>-11,88; 46,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,44; 65,88</t>
+          <t>17,06; 66,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 29,11</t>
+          <t>-11,47; 28,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 28,81</t>
+          <t>-7,29; 30,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,58</t>
+          <t>1,42; 10,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,72; -0,29</t>
+          <t>-8,47; -0,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,93; -5,31</t>
+          <t>-16,67; -5,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,21</t>
+          <t>4,03; 10,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 4,03</t>
+          <t>-2,33; 4,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,66</t>
+          <t>-3,19; 2,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,65</t>
+          <t>3,93; 9,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,98</t>
+          <t>-4,47; 0,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,21; -2,17</t>
+          <t>-9,15; -2,19</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 51,65</t>
+          <t>5,85; 56,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,92; -1,68</t>
+          <t>-36,75; -1,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,89; -27,98</t>
+          <t>-73,14; -28,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,84; 104,29</t>
+          <t>29,21; 105,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 37,16</t>
+          <t>-17,37; 39,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 26,18</t>
+          <t>-23,25; 23,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,24; 65,73</t>
+          <t>21,76; 62,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 6,52</t>
+          <t>-25,19; 5,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -14,75</t>
+          <t>-54,13; -14,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 9,82</t>
+          <t>-0,39; 9,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,71</t>
+          <t>-5,87; 3,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -4,38</t>
+          <t>-13,62; -4,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 2,49</t>
+          <t>-6,25; 2,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,14; -1,88</t>
+          <t>-9,87; -1,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -7,36</t>
+          <t>-16,8; -7,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,64</t>
+          <t>-1,97; 4,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -0,48</t>
+          <t>-6,69; -0,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,21; -7,32</t>
+          <t>-13,99; -7,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 56,18</t>
+          <t>-2,18; 51,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 21,49</t>
+          <t>-26,1; 22,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,52; -25,04</t>
+          <t>-59,4; -27,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 16,83</t>
+          <t>-30,66; 15,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,39; -11,34</t>
+          <t>-50,69; -10,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,7; -45,9</t>
+          <t>-81,88; -46,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 27,95</t>
+          <t>-9,42; 25,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,12; -2,76</t>
+          <t>-33,13; -1,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,72; -42,48</t>
+          <t>-71,01; -43,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 4,27</t>
+          <t>-3,63; 4,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 1,88</t>
+          <t>-5,39; 2,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,59</t>
+          <t>-5,81; 1,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 4,45</t>
+          <t>-2,6; 4,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 0,99</t>
+          <t>-6,56; 0,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,59; -3,1</t>
+          <t>-9,7; -3,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,4</t>
+          <t>-1,88; 3,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,19</t>
+          <t>-4,94; -0,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -2,04</t>
+          <t>-6,72; -1,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 25,81</t>
+          <t>-18,26; 28,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 11,89</t>
+          <t>-26,87; 16,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 9,98</t>
+          <t>-28,02; 11,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 30,71</t>
+          <t>-14,29; 31,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 8,79</t>
+          <t>-36,83; 4,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,08; -22,01</t>
+          <t>-54,28; -23,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 21,93</t>
+          <t>-10,61; 20,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 1,28</t>
+          <t>-27,63; -0,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,66; -13,16</t>
+          <t>-36,62; -11,22</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,2</t>
+          <t>2,52; 7,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,14</t>
+          <t>-4,17; 0,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -3,18</t>
+          <t>-8,61; -3,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,68</t>
+          <t>0,98; 4,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,16</t>
+          <t>-3,55; 0,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,6; -2,49</t>
+          <t>-6,57; -2,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,38</t>
+          <t>2,21; 5,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,37</t>
+          <t>-3,19; -0,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,54; -3,18</t>
+          <t>-6,47; -3,15</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12,62; 38,29</t>
+          <t>12,37; 37,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 0,77</t>
+          <t>-20,25; 0,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,77; -16,69</t>
+          <t>-43,49; -17,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6,15; 34,4</t>
+          <t>6,27; 35,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 1,08</t>
+          <t>-23,02; 1,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,44; -18,24</t>
+          <t>-42,41; -18,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,99; 32,41</t>
+          <t>12,21; 32,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,37; -2,27</t>
+          <t>-17,79; -2,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-37,57; -19,33</t>
+          <t>-36,86; -19,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C04-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C04-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 14,51</t>
+          <t>4,26; 14,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 5,24</t>
+          <t>-5,2; 5,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 5,97</t>
+          <t>-4,01; 6,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 8,05</t>
+          <t>-0,19; 8,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 5,03</t>
+          <t>-2,84; 5,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 5,21</t>
+          <t>-1,85; 4,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 10,27</t>
+          <t>3,51; 10,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 4,3</t>
+          <t>-2,61; 4,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 4,78</t>
+          <t>-1,46; 4,66</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 76,79</t>
+          <t>17,52; 75,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 27,71</t>
+          <t>-21,7; 29,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 33,11</t>
+          <t>-16,02; 32,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 69,52</t>
+          <t>-1,51; 69,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 43,88</t>
+          <t>-18,77; 45,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 46,84</t>
+          <t>-11,18; 43,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 66,07</t>
+          <t>17,76; 64,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 28,38</t>
+          <t>-13,59; 28,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 30,42</t>
+          <t>-7,98; 30,06</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-9,72</t>
+          <t>-5,96</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,81</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 10,21</t>
+          <t>0,95; 9,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -0,27</t>
+          <t>-8,71; -0,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,67; -5,38</t>
+          <t>-9,83; -2,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,9</t>
+          <t>3,83; 11,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,19</t>
+          <t>-2,38; 4,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,44</t>
+          <t>-2,92; 2,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 9,4</t>
+          <t>3,45; 9,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,88</t>
+          <t>-4,14; 0,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,15; -2,19</t>
+          <t>-4,99; -0,32</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-46,78%</t>
+          <t>-28,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,3%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-29,63%</t>
+          <t>-17,05%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 56,07</t>
+          <t>3,68; 51,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,75; -1,06</t>
+          <t>-37,68; -3,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,14; -28,14</t>
+          <t>-42,84; -12,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,21; 105,58</t>
+          <t>27,83; 109,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 39,65</t>
+          <t>-16,97; 41,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 23,84</t>
+          <t>-20,57; 27,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,76; 62,24</t>
+          <t>19,65; 64,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 5,91</t>
+          <t>-24,1; 5,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,13; -14,06</t>
+          <t>-28,93; -1,86</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-9,09</t>
+          <t>-8,19</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,89</t>
+          <t>-8,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,27</t>
+          <t>-8,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 9,6</t>
+          <t>0,02; 10,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 3,89</t>
+          <t>-5,65; 3,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,62; -4,71</t>
+          <t>-12,5; -3,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 2,35</t>
+          <t>-5,76; 2,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,87; -1,8</t>
+          <t>-10,06; -1,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,8; -7,51</t>
+          <t>-12,15; -4,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 4,44</t>
+          <t>-2,13; 4,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,69; -0,25</t>
+          <t>-6,81; -0,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -7,45</t>
+          <t>-11,37; -5,89</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-45,36%</t>
+          <t>-40,87%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-62,44%</t>
+          <t>-49,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-54,92%</t>
+          <t>-44,93%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 51,67</t>
+          <t>-1,21; 54,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 22,65</t>
+          <t>-25,59; 24,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,4; -27,1</t>
+          <t>-55,76; -19,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 15,76</t>
+          <t>-28,9; 17,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,69; -10,93</t>
+          <t>-51,25; -12,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,88; -46,21</t>
+          <t>-61,85; -32,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 25,82</t>
+          <t>-10,23; 25,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,13; -1,37</t>
+          <t>-33,48; -2,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,01; -43,1</t>
+          <t>-54,78; -34,07</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,24</t>
+          <t>-5,54</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,24</t>
+          <t>-3,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,42</t>
+          <t>-3,57; 4,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 2,67</t>
+          <t>-5,63; 1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 1,84</t>
+          <t>-4,63; 3,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,4</t>
+          <t>-2,71; 4,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 0,57</t>
+          <t>-6,59; 0,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,7; -3,27</t>
+          <t>-8,81; -2,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,23</t>
+          <t>-2,09; 3,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,14</t>
+          <t>-4,84; 0,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,72; -1,71</t>
+          <t>-5,62; -0,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,01%</t>
+          <t>-3,23%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-39,16%</t>
+          <t>-34,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-25,1%</t>
+          <t>-19,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 28,25</t>
+          <t>-17,73; 27,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 16,54</t>
+          <t>-28,13; 10,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 11,69</t>
+          <t>-23,33; 19,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 31,06</t>
+          <t>-15,19; 31,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 4,34</t>
+          <t>-36,8; 1,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,28; -23,34</t>
+          <t>-47,79; -18,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 20,71</t>
+          <t>-11,34; 21,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,63; -0,86</t>
+          <t>-26,66; 0,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,62; -11,22</t>
+          <t>-30,34; -5,69</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,17</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-3,32</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,13</t>
+          <t>2,46; 7,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,13</t>
+          <t>-4,02; 0,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,61; -3,2</t>
+          <t>-5,81; -1,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,74</t>
+          <t>1,04; 4,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,22</t>
+          <t>-3,51; 0,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,57; -2,5</t>
+          <t>-4,9; -1,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,3</t>
+          <t>2,27; 5,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,34</t>
+          <t>-3,51; -0,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -3,15</t>
+          <t>-4,56; -2,07</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-27,5%</t>
+          <t>-17,95%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-28,39%</t>
+          <t>-21,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-27,64%</t>
+          <t>-19,31%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12,37; 37,62</t>
+          <t>11,63; 37,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 0,53</t>
+          <t>-19,34; 1,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,49; -17,26</t>
+          <t>-27,19; -8,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6,27; 35,02</t>
+          <t>6,6; 35,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 1,65</t>
+          <t>-22,41; 1,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -18,18</t>
+          <t>-30,54; -12,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,21; 32,94</t>
+          <t>12,47; 31,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -2,1</t>
+          <t>-19,17; -2,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-36,86; -19,06</t>
+          <t>-25,4; -12,53</t>
         </is>
       </c>
     </row>
